--- a/data collection/motor-speed-calibration.xlsx
+++ b/data collection/motor-speed-calibration.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/medina_colabrese_epfl_ch/Documents/0 Mobile Robots/EPFL-BOMR-Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/medina_colabrese_epfl_ch/Documents/0 Mobile Robots/EPFL-BOMR-Project/data collection/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_F25DC773A252ABDACC1048DE419B6E6A5ADE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DB5E762-0E8A-401E-9110-0C8BE53D7EA5}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_F25DC773A252ABDACC1048DE419B6E6A5ADE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9CE837C-D7C4-4B41-BF3D-1E7FDFEBCE1A}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,10 +27,29 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>Thymio speed</t>
+  </si>
+  <si>
+    <t>Real speed</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -58,10 +77,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -94,6 +114,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-CA"/>
+              <a:t>Thymio units to mm/s</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -199,8 +244,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-0.11034534805505881"/>
-                  <c:y val="-4.2274223830046219E-2"/>
+                  <c:x val="-0.1619846584597486"/>
+                  <c:y val="1.3740994552802671E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -1179,6 +1224,66 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-CA"/>
+                  <a:t>Speed in Thymio</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-CA" baseline="0"/>
+                  <a:t> Units</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-CA"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1241,6 +1346,61 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-CA"/>
+                  <a:t>Speed in mm/s</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1894,16 +2054,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>525780</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>146685</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>74294</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>617220</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>146685</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>632460</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>30479</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1936,1199 +2096,11 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="speed_to_mtr_input(1)"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="A1">
-            <v>100</v>
-          </cell>
-          <cell r="B1">
-            <v>37.947349548339801</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2">
-            <v>100</v>
-          </cell>
-          <cell r="B2">
-            <v>37.556003570556598</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3">
-            <v>100</v>
-          </cell>
-          <cell r="B3">
-            <v>37.632308959960902</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4">
-            <v>100</v>
-          </cell>
-          <cell r="B4">
-            <v>38.003692626953097</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>100</v>
-          </cell>
-          <cell r="B5">
-            <v>38.146640777587798</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>100</v>
-          </cell>
-          <cell r="B6">
-            <v>38.1280517578125</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>100</v>
-          </cell>
-          <cell r="B7">
-            <v>37.583938598632798</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>100</v>
-          </cell>
-          <cell r="B8">
-            <v>37.675132751464801</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>100</v>
-          </cell>
-          <cell r="B9">
-            <v>37.696113586425703</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>100</v>
-          </cell>
-          <cell r="B10">
-            <v>37.936565399169901</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>100</v>
-          </cell>
-          <cell r="B11">
-            <v>37.761936187744098</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>100</v>
-          </cell>
-          <cell r="B12">
-            <v>37.9704780578613</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>100</v>
-          </cell>
-          <cell r="B13">
-            <v>38.2182006835937</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>100</v>
-          </cell>
-          <cell r="B14">
-            <v>37.825279235839801</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>100</v>
-          </cell>
-          <cell r="B15">
-            <v>37.765293121337798</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>100</v>
-          </cell>
-          <cell r="B16">
-            <v>38.033489227294901</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17">
-            <v>200</v>
-          </cell>
-          <cell r="B17">
-            <v>72.826713562011705</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18">
-            <v>200</v>
-          </cell>
-          <cell r="B18">
-            <v>73.202110290527301</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19">
-            <v>200</v>
-          </cell>
-          <cell r="B19">
-            <v>72.882095336914006</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20">
-            <v>200</v>
-          </cell>
-          <cell r="B20">
-            <v>72.969741821289006</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21">
-            <v>200</v>
-          </cell>
-          <cell r="B21">
-            <v>74.181671142578097</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22">
-            <v>200</v>
-          </cell>
-          <cell r="B22">
-            <v>74.268722534179602</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23">
-            <v>200</v>
-          </cell>
-          <cell r="B23">
-            <v>74.175796508789006</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24">
-            <v>200</v>
-          </cell>
-          <cell r="B24">
-            <v>74.154914855957003</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25">
-            <v>200</v>
-          </cell>
-          <cell r="B25">
-            <v>73.212623596191406</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26">
-            <v>200</v>
-          </cell>
-          <cell r="B26">
-            <v>73.144989013671804</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27">
-            <v>200</v>
-          </cell>
-          <cell r="B27">
-            <v>73.111770629882798</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28">
-            <v>200</v>
-          </cell>
-          <cell r="B28">
-            <v>74.314620971679602</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29">
-            <v>200</v>
-          </cell>
-          <cell r="B29">
-            <v>73.072647094726506</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30">
-            <v>200</v>
-          </cell>
-          <cell r="B30">
-            <v>74.056419372558594</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31">
-            <v>200</v>
-          </cell>
-          <cell r="B31">
-            <v>72.906921386718693</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32">
-            <v>200</v>
-          </cell>
-          <cell r="B32">
-            <v>73.103477478027301</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33">
-            <v>150</v>
-          </cell>
-          <cell r="B33">
-            <v>55.245311737060497</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34">
-            <v>150</v>
-          </cell>
-          <cell r="B34">
-            <v>55.275917053222599</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35">
-            <v>150</v>
-          </cell>
-          <cell r="B35">
-            <v>55.483909606933501</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36">
-            <v>150</v>
-          </cell>
-          <cell r="B36">
-            <v>56.253856658935497</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37">
-            <v>150</v>
-          </cell>
-          <cell r="B37">
-            <v>55.359550476074197</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38">
-            <v>150</v>
-          </cell>
-          <cell r="B38">
-            <v>55.344108581542898</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39">
-            <v>150</v>
-          </cell>
-          <cell r="B39">
-            <v>55.358131408691399</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40">
-            <v>150</v>
-          </cell>
-          <cell r="B40">
-            <v>55.611400604247997</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41">
-            <v>150</v>
-          </cell>
-          <cell r="B41">
-            <v>56.211162567138601</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42">
-            <v>150</v>
-          </cell>
-          <cell r="B42">
-            <v>55.528358459472599</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43">
-            <v>110</v>
-          </cell>
-          <cell r="B43">
-            <v>41.489864349365199</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44">
-            <v>110</v>
-          </cell>
-          <cell r="B44">
-            <v>41.4398384094238</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45">
-            <v>110</v>
-          </cell>
-          <cell r="B45">
-            <v>42.135780334472599</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46">
-            <v>120</v>
-          </cell>
-          <cell r="B46">
-            <v>44.103515625</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47">
-            <v>120</v>
-          </cell>
-          <cell r="B47">
-            <v>45.042484283447202</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48">
-            <v>130</v>
-          </cell>
-          <cell r="B48">
-            <v>48.931404113769503</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49">
-            <v>130</v>
-          </cell>
-          <cell r="B49">
-            <v>48.868927001953097</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50">
-            <v>130</v>
-          </cell>
-          <cell r="B50">
-            <v>49.004451751708899</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51">
-            <v>140</v>
-          </cell>
-          <cell r="B51">
-            <v>52.148784637451101</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52">
-            <v>140</v>
-          </cell>
-          <cell r="B52">
-            <v>53.0572700500488</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53">
-            <v>140</v>
-          </cell>
-          <cell r="B53">
-            <v>53.1823120117187</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="A54">
-            <v>140</v>
-          </cell>
-          <cell r="B54">
-            <v>52.349220275878899</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="A55">
-            <v>160</v>
-          </cell>
-          <cell r="B55">
-            <v>59.2225341796875</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="A56">
-            <v>160</v>
-          </cell>
-          <cell r="B56">
-            <v>60.133373260497997</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="A57">
-            <v>160</v>
-          </cell>
-          <cell r="B57">
-            <v>58.945873260497997</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="A58">
-            <v>180</v>
-          </cell>
-          <cell r="B58">
-            <v>66.761428833007798</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="A59">
-            <v>180</v>
-          </cell>
-          <cell r="B59">
-            <v>68.363746643066406</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="A60">
-            <v>180</v>
-          </cell>
-          <cell r="B60">
-            <v>67.231178283691406</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="A61">
-            <v>190</v>
-          </cell>
-          <cell r="B61">
-            <v>71.097145080566406</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="A62">
-            <v>190</v>
-          </cell>
-          <cell r="B62">
-            <v>70.110191345214801</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="A63">
-            <v>190</v>
-          </cell>
-          <cell r="B63">
-            <v>69.957695007324205</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="A64">
-            <v>225</v>
-          </cell>
-          <cell r="B64">
-            <v>84.250335693359304</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="A65">
-            <v>225</v>
-          </cell>
-          <cell r="B65">
-            <v>82.887565612792898</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="A66">
-            <v>225</v>
-          </cell>
-          <cell r="B66">
-            <v>83.120491027832003</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="A67">
-            <v>225</v>
-          </cell>
-          <cell r="B67">
-            <v>82.969505310058594</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="A68">
-            <v>225</v>
-          </cell>
-          <cell r="B68">
-            <v>84.640823364257798</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="A69">
-            <v>225</v>
-          </cell>
-          <cell r="B69">
-            <v>83.370384216308594</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="A70">
-            <v>250</v>
-          </cell>
-          <cell r="B70">
-            <v>92.075706481933594</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="A71">
-            <v>250</v>
-          </cell>
-          <cell r="B71">
-            <v>90.467185974121094</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="A72">
-            <v>250</v>
-          </cell>
-          <cell r="B72">
-            <v>90.876480102539006</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="A73">
-            <v>250</v>
-          </cell>
-          <cell r="B73">
-            <v>91.030120849609304</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="A74">
-            <v>250</v>
-          </cell>
-          <cell r="B74">
-            <v>91.1021728515625</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="A75">
-            <v>250</v>
-          </cell>
-          <cell r="B75">
-            <v>90.482322692871094</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="A76">
-            <v>250</v>
-          </cell>
-          <cell r="B76">
-            <v>91.2183837890625</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="A77">
-            <v>250</v>
-          </cell>
-          <cell r="B77">
-            <v>90.765350341796804</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="A78">
-            <v>275</v>
-          </cell>
-          <cell r="B78">
-            <v>98.324745178222599</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="A79">
-            <v>275</v>
-          </cell>
-          <cell r="B79">
-            <v>97.644721984863196</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="A80">
-            <v>275</v>
-          </cell>
-          <cell r="B80">
-            <v>98.625343322753906</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="A81">
-            <v>275</v>
-          </cell>
-          <cell r="B81">
-            <v>98.048446655273395</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="A82">
-            <v>275</v>
-          </cell>
-          <cell r="B82">
-            <v>97.541885375976506</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="A83">
-            <v>275</v>
-          </cell>
-          <cell r="B83">
-            <v>98.221984863281193</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="A84">
-            <v>275</v>
-          </cell>
-          <cell r="B84">
-            <v>98.3951416015625</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="A85">
-            <v>300</v>
-          </cell>
-          <cell r="B85">
-            <v>112.94920349121</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="A86">
-            <v>300</v>
-          </cell>
-          <cell r="B86">
-            <v>111.3111038208</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="A87">
-            <v>300</v>
-          </cell>
-          <cell r="B87">
-            <v>111.458618164062</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="A88">
-            <v>300</v>
-          </cell>
-          <cell r="B88">
-            <v>112.343132019042</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="A89">
-            <v>300</v>
-          </cell>
-          <cell r="B89">
-            <v>113.33374786376901</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="A90">
-            <v>300</v>
-          </cell>
-          <cell r="B90">
-            <v>111.86164855957</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="A91">
-            <v>300</v>
-          </cell>
-          <cell r="B91">
-            <v>112.181800842285</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="A92">
-            <v>300</v>
-          </cell>
-          <cell r="B92">
-            <v>112.669151306152</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="A93">
-            <v>325</v>
-          </cell>
-          <cell r="B93">
-            <v>119.597518920898</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="A94">
-            <v>325</v>
-          </cell>
-          <cell r="B94">
-            <v>119.668937683105</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="A95">
-            <v>325</v>
-          </cell>
-          <cell r="B95">
-            <v>118.55248260498</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="A96">
-            <v>325</v>
-          </cell>
-          <cell r="B96">
-            <v>120.087356567382</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="A97">
-            <v>325</v>
-          </cell>
-          <cell r="B97">
-            <v>120.041015625</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="A98">
-            <v>325</v>
-          </cell>
-          <cell r="B98">
-            <v>117.07137298583901</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="A99">
-            <v>325</v>
-          </cell>
-          <cell r="B99">
-            <v>116.49659729003901</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="A100">
-            <v>325</v>
-          </cell>
-          <cell r="B100">
-            <v>119.387168884277</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="A101">
-            <v>350</v>
-          </cell>
-          <cell r="B101">
-            <v>134.02989196777301</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="A102">
-            <v>350</v>
-          </cell>
-          <cell r="B102">
-            <v>129.77296447753901</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="A103">
-            <v>350</v>
-          </cell>
-          <cell r="B103">
-            <v>129.58163452148401</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="A104">
-            <v>350</v>
-          </cell>
-          <cell r="B104">
-            <v>129.39317321777301</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="A105">
-            <v>350</v>
-          </cell>
-          <cell r="B105">
-            <v>131.60490417480401</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="A106">
-            <v>350</v>
-          </cell>
-          <cell r="B106">
-            <v>128.85876464843699</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="A107">
-            <v>350</v>
-          </cell>
-          <cell r="B107">
-            <v>130.38032531738199</v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="A108">
-            <v>350</v>
-          </cell>
-          <cell r="B108">
-            <v>129.2626953125</v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="A109">
-            <v>375</v>
-          </cell>
-          <cell r="B109">
-            <v>141.05140686035099</v>
-          </cell>
-        </row>
-        <row r="110">
-          <cell r="A110">
-            <v>375</v>
-          </cell>
-          <cell r="B110">
-            <v>139.86647033691401</v>
-          </cell>
-        </row>
-        <row r="111">
-          <cell r="A111">
-            <v>375</v>
-          </cell>
-          <cell r="B111">
-            <v>139.86706542968699</v>
-          </cell>
-        </row>
-        <row r="112">
-          <cell r="A112">
-            <v>375</v>
-          </cell>
-          <cell r="B112">
-            <v>139.56504821777301</v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="A113">
-            <v>375</v>
-          </cell>
-          <cell r="B113">
-            <v>141.54527282714801</v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="A114">
-            <v>375</v>
-          </cell>
-          <cell r="B114">
-            <v>139.04574584960901</v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="A115">
-            <v>375</v>
-          </cell>
-          <cell r="B115">
-            <v>140.45903015136699</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="A116">
-            <v>375</v>
-          </cell>
-          <cell r="B116">
-            <v>139.50605773925699</v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="A117">
-            <v>400</v>
-          </cell>
-          <cell r="B117">
-            <v>152.88243103027301</v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="A118">
-            <v>400</v>
-          </cell>
-          <cell r="B118">
-            <v>146.42054748535099</v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="A119">
-            <v>400</v>
-          </cell>
-          <cell r="B119">
-            <v>147.19046020507801</v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="A120">
-            <v>400</v>
-          </cell>
-          <cell r="B120">
-            <v>146.21650695800699</v>
-          </cell>
-        </row>
-        <row r="121">
-          <cell r="A121">
-            <v>400</v>
-          </cell>
-          <cell r="B121">
-            <v>152.85513305664</v>
-          </cell>
-        </row>
-        <row r="122">
-          <cell r="A122">
-            <v>400</v>
-          </cell>
-          <cell r="B122">
-            <v>147.08241271972599</v>
-          </cell>
-        </row>
-        <row r="123">
-          <cell r="A123">
-            <v>400</v>
-          </cell>
-          <cell r="B123">
-            <v>148.21440124511699</v>
-          </cell>
-        </row>
-        <row r="124">
-          <cell r="A124">
-            <v>400</v>
-          </cell>
-          <cell r="B124">
-            <v>146.92153930664</v>
-          </cell>
-        </row>
-        <row r="125">
-          <cell r="A125">
-            <v>425</v>
-          </cell>
-          <cell r="B125">
-            <v>157.809967041015</v>
-          </cell>
-        </row>
-        <row r="126">
-          <cell r="A126">
-            <v>425</v>
-          </cell>
-          <cell r="B126">
-            <v>149.60018920898401</v>
-          </cell>
-        </row>
-        <row r="127">
-          <cell r="A127">
-            <v>425</v>
-          </cell>
-          <cell r="B127">
-            <v>151.85455322265599</v>
-          </cell>
-        </row>
-        <row r="128">
-          <cell r="A128">
-            <v>425</v>
-          </cell>
-          <cell r="B128">
-            <v>149.95365905761699</v>
-          </cell>
-        </row>
-        <row r="129">
-          <cell r="A129">
-            <v>425</v>
-          </cell>
-          <cell r="B129">
-            <v>157.86619567871</v>
-          </cell>
-        </row>
-        <row r="130">
-          <cell r="A130">
-            <v>425</v>
-          </cell>
-          <cell r="B130">
-            <v>151.080307006835</v>
-          </cell>
-        </row>
-        <row r="131">
-          <cell r="A131">
-            <v>425</v>
-          </cell>
-          <cell r="B131">
-            <v>151.45597839355401</v>
-          </cell>
-        </row>
-        <row r="132">
-          <cell r="A132">
-            <v>425</v>
-          </cell>
-          <cell r="B132">
-            <v>151.01095581054599</v>
-          </cell>
-        </row>
-        <row r="133">
-          <cell r="A133">
-            <v>450</v>
-          </cell>
-          <cell r="B133">
-            <v>166.29953002929599</v>
-          </cell>
-        </row>
-        <row r="134">
-          <cell r="A134">
-            <v>450</v>
-          </cell>
-          <cell r="B134">
-            <v>157.990142822265</v>
-          </cell>
-        </row>
-        <row r="135">
-          <cell r="A135">
-            <v>450</v>
-          </cell>
-          <cell r="B135">
-            <v>160.46636962890599</v>
-          </cell>
-        </row>
-        <row r="136">
-          <cell r="A136">
-            <v>450</v>
-          </cell>
-          <cell r="B136">
-            <v>158.114486694335</v>
-          </cell>
-        </row>
-        <row r="137">
-          <cell r="A137">
-            <v>450</v>
-          </cell>
-          <cell r="B137">
-            <v>164.97518920898401</v>
-          </cell>
-        </row>
-        <row r="138">
-          <cell r="A138">
-            <v>450</v>
-          </cell>
-          <cell r="B138">
-            <v>157.52406311035099</v>
-          </cell>
-        </row>
-        <row r="139">
-          <cell r="A139">
-            <v>450</v>
-          </cell>
-          <cell r="B139">
-            <v>159.21244812011699</v>
-          </cell>
-        </row>
-        <row r="140">
-          <cell r="A140">
-            <v>450</v>
-          </cell>
-          <cell r="B140">
-            <v>156.62593078613199</v>
-          </cell>
-        </row>
-        <row r="141">
-          <cell r="A141">
-            <v>75</v>
-          </cell>
-          <cell r="B141">
-            <v>30.01362991333</v>
-          </cell>
-        </row>
-        <row r="142">
-          <cell r="A142">
-            <v>75</v>
-          </cell>
-          <cell r="B142">
-            <v>26.8815097808837</v>
-          </cell>
-        </row>
-        <row r="143">
-          <cell r="A143">
-            <v>75</v>
-          </cell>
-          <cell r="B143">
-            <v>29.338521957397401</v>
-          </cell>
-        </row>
-        <row r="144">
-          <cell r="A144">
-            <v>75</v>
-          </cell>
-          <cell r="B144">
-            <v>26.9236145019531</v>
-          </cell>
-        </row>
-        <row r="145">
-          <cell r="A145">
-            <v>75</v>
-          </cell>
-          <cell r="B145">
-            <v>29.346654891967699</v>
-          </cell>
-        </row>
-        <row r="146">
-          <cell r="A146">
-            <v>75</v>
-          </cell>
-          <cell r="B146">
-            <v>26.952102661132798</v>
-          </cell>
-        </row>
-        <row r="147">
-          <cell r="A147">
-            <v>75</v>
-          </cell>
-          <cell r="B147">
-            <v>29.3502292633056</v>
-          </cell>
-        </row>
-        <row r="148">
-          <cell r="A148">
-            <v>75</v>
-          </cell>
-          <cell r="B148">
-            <v>26.5060520172119</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="0" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3397,19 +2369,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B148"/>
+  <dimension ref="A1:B149"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="9.20703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.83984375" style="1"/>
+    <col min="1" max="1" width="12.05078125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5234375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="1">
-        <v>100</v>
-      </c>
-      <c r="B1" s="2">
-        <v>37.947349548339801</v>
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3417,7 +2389,7 @@
         <v>100</v>
       </c>
       <c r="B2" s="2">
-        <v>37.556003570556598</v>
+        <v>37.947349548339801</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3425,7 +2397,7 @@
         <v>100</v>
       </c>
       <c r="B3" s="2">
-        <v>37.632308959960902</v>
+        <v>37.556003570556598</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3433,23 +2405,23 @@
         <v>100</v>
       </c>
       <c r="B4" s="2">
-        <v>38.003692626953097</v>
+        <v>37.632308959960902</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1">
         <v>100</v>
       </c>
-      <c r="B5" s="1">
-        <v>38.146640777587798</v>
+      <c r="B5" s="2">
+        <v>38.003692626953097</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1">
         <v>100</v>
       </c>
-      <c r="B6" s="2">
-        <v>38.1280517578125</v>
+      <c r="B6" s="1">
+        <v>38.146640777587798</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3457,7 +2429,7 @@
         <v>100</v>
       </c>
       <c r="B7" s="2">
-        <v>37.583938598632798</v>
+        <v>38.1280517578125</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3465,7 +2437,7 @@
         <v>100</v>
       </c>
       <c r="B8" s="2">
-        <v>37.675132751464801</v>
+        <v>37.583938598632798</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3473,7 +2445,7 @@
         <v>100</v>
       </c>
       <c r="B9" s="2">
-        <v>37.696113586425703</v>
+        <v>37.675132751464801</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3481,7 +2453,7 @@
         <v>100</v>
       </c>
       <c r="B10" s="2">
-        <v>37.936565399169901</v>
+        <v>37.696113586425703</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3489,7 +2461,7 @@
         <v>100</v>
       </c>
       <c r="B11" s="2">
-        <v>37.761936187744098</v>
+        <v>37.936565399169901</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3497,7 +2469,7 @@
         <v>100</v>
       </c>
       <c r="B12" s="2">
-        <v>37.9704780578613</v>
+        <v>37.761936187744098</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3505,7 +2477,7 @@
         <v>100</v>
       </c>
       <c r="B13" s="2">
-        <v>38.2182006835937</v>
+        <v>37.9704780578613</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3513,7 +2485,7 @@
         <v>100</v>
       </c>
       <c r="B14" s="2">
-        <v>37.825279235839801</v>
+        <v>38.2182006835937</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3521,7 +2493,7 @@
         <v>100</v>
       </c>
       <c r="B15" s="2">
-        <v>37.765293121337798</v>
+        <v>37.825279235839801</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3529,15 +2501,15 @@
         <v>100</v>
       </c>
       <c r="B16" s="2">
-        <v>38.033489227294901</v>
+        <v>37.765293121337798</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="B17" s="2">
-        <v>72.826713562011705</v>
+        <v>38.033489227294901</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3545,7 +2517,7 @@
         <v>200</v>
       </c>
       <c r="B18" s="2">
-        <v>73.202110290527301</v>
+        <v>72.826713562011705</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3553,7 +2525,7 @@
         <v>200</v>
       </c>
       <c r="B19" s="2">
-        <v>72.882095336914006</v>
+        <v>73.202110290527301</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3561,7 +2533,7 @@
         <v>200</v>
       </c>
       <c r="B20" s="2">
-        <v>72.969741821289006</v>
+        <v>72.882095336914006</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3569,7 +2541,7 @@
         <v>200</v>
       </c>
       <c r="B21" s="2">
-        <v>74.181671142578097</v>
+        <v>72.969741821289006</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3577,7 +2549,7 @@
         <v>200</v>
       </c>
       <c r="B22" s="2">
-        <v>74.268722534179602</v>
+        <v>74.181671142578097</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3585,23 +2557,23 @@
         <v>200</v>
       </c>
       <c r="B23" s="2">
-        <v>74.175796508789006</v>
+        <v>74.268722534179602</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1">
         <v>200</v>
       </c>
-      <c r="B24" s="1">
-        <v>74.154914855957003</v>
+      <c r="B24" s="2">
+        <v>74.175796508789006</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1">
         <v>200</v>
       </c>
-      <c r="B25" s="2">
-        <v>73.212623596191406</v>
+      <c r="B25" s="1">
+        <v>74.154914855957003</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3609,7 +2581,7 @@
         <v>200</v>
       </c>
       <c r="B26" s="2">
-        <v>73.144989013671804</v>
+        <v>73.212623596191406</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3617,7 +2589,7 @@
         <v>200</v>
       </c>
       <c r="B27" s="2">
-        <v>73.111770629882798</v>
+        <v>73.144989013671804</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3625,23 +2597,23 @@
         <v>200</v>
       </c>
       <c r="B28" s="2">
-        <v>74.314620971679602</v>
+        <v>73.111770629882798</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1">
         <v>200</v>
       </c>
-      <c r="B29" s="1">
-        <v>73.072647094726506</v>
+      <c r="B29" s="2">
+        <v>74.314620971679602</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1">
         <v>200</v>
       </c>
-      <c r="B30" s="2">
-        <v>74.056419372558594</v>
+      <c r="B30" s="1">
+        <v>73.072647094726506</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3649,7 +2621,7 @@
         <v>200</v>
       </c>
       <c r="B31" s="2">
-        <v>72.906921386718693</v>
+        <v>74.056419372558594</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3657,15 +2629,15 @@
         <v>200</v>
       </c>
       <c r="B32" s="2">
-        <v>73.103477478027301</v>
+        <v>72.906921386718693</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="1">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="B33" s="2">
-        <v>55.245311737060497</v>
+        <v>73.103477478027301</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3673,7 +2645,7 @@
         <v>150</v>
       </c>
       <c r="B34" s="2">
-        <v>55.275917053222599</v>
+        <v>55.245311737060497</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3681,7 +2653,7 @@
         <v>150</v>
       </c>
       <c r="B35" s="2">
-        <v>55.483909606933501</v>
+        <v>55.275917053222599</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3689,7 +2661,7 @@
         <v>150</v>
       </c>
       <c r="B36" s="2">
-        <v>56.253856658935497</v>
+        <v>55.483909606933501</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3697,7 +2669,7 @@
         <v>150</v>
       </c>
       <c r="B37" s="2">
-        <v>55.359550476074197</v>
+        <v>56.253856658935497</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3705,7 +2677,7 @@
         <v>150</v>
       </c>
       <c r="B38" s="2">
-        <v>55.344108581542898</v>
+        <v>55.359550476074197</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3713,7 +2685,7 @@
         <v>150</v>
       </c>
       <c r="B39" s="2">
-        <v>55.358131408691399</v>
+        <v>55.344108581542898</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3721,7 +2693,7 @@
         <v>150</v>
       </c>
       <c r="B40" s="2">
-        <v>55.611400604247997</v>
+        <v>55.358131408691399</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3729,7 +2701,7 @@
         <v>150</v>
       </c>
       <c r="B41" s="2">
-        <v>56.211162567138601</v>
+        <v>55.611400604247997</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3737,15 +2709,15 @@
         <v>150</v>
       </c>
       <c r="B42" s="2">
-        <v>55.528358459472599</v>
+        <v>56.211162567138601</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="1">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="B43" s="2">
-        <v>41.489864349365199</v>
+        <v>55.528358459472599</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3753,23 +2725,23 @@
         <v>110</v>
       </c>
       <c r="B44" s="2">
-        <v>41.4398384094238</v>
+        <v>41.489864349365199</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="1">
         <v>110</v>
       </c>
-      <c r="B45" s="1">
-        <v>42.135780334472599</v>
+      <c r="B45" s="2">
+        <v>41.4398384094238</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="1">
-        <v>120</v>
-      </c>
-      <c r="B46" s="2">
-        <v>44.103515625</v>
+        <v>110</v>
+      </c>
+      <c r="B46" s="1">
+        <v>42.135780334472599</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3777,15 +2749,15 @@
         <v>120</v>
       </c>
       <c r="B47" s="2">
-        <v>45.042484283447202</v>
+        <v>44.103515625</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="1">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B48" s="2">
-        <v>48.931404113769503</v>
+        <v>45.042484283447202</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3793,7 +2765,7 @@
         <v>130</v>
       </c>
       <c r="B49" s="2">
-        <v>48.868927001953097</v>
+        <v>48.931404113769503</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3801,15 +2773,15 @@
         <v>130</v>
       </c>
       <c r="B50" s="2">
-        <v>49.004451751708899</v>
+        <v>48.868927001953097</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="1">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B51" s="2">
-        <v>52.148784637451101</v>
+        <v>49.004451751708899</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3817,7 +2789,7 @@
         <v>140</v>
       </c>
       <c r="B52" s="2">
-        <v>53.0572700500488</v>
+        <v>52.148784637451101</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3825,23 +2797,23 @@
         <v>140</v>
       </c>
       <c r="B53" s="2">
-        <v>53.1823120117187</v>
+        <v>53.0572700500488</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="1">
         <v>140</v>
       </c>
-      <c r="B54" s="1">
-        <v>52.349220275878899</v>
+      <c r="B54" s="2">
+        <v>53.1823120117187</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1">
-        <v>160</v>
-      </c>
-      <c r="B55" s="2">
-        <v>59.2225341796875</v>
+        <v>140</v>
+      </c>
+      <c r="B55" s="1">
+        <v>52.349220275878899</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3849,7 +2821,7 @@
         <v>160</v>
       </c>
       <c r="B56" s="2">
-        <v>60.133373260497997</v>
+        <v>59.2225341796875</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3857,15 +2829,15 @@
         <v>160</v>
       </c>
       <c r="B57" s="2">
-        <v>58.945873260497997</v>
+        <v>60.133373260497997</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="1">
-        <v>180</v>
-      </c>
-      <c r="B58" s="1">
-        <v>66.761428833007798</v>
+        <v>160</v>
+      </c>
+      <c r="B58" s="2">
+        <v>58.945873260497997</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3873,7 +2845,7 @@
         <v>180</v>
       </c>
       <c r="B59" s="1">
-        <v>68.363746643066406</v>
+        <v>66.761428833007798</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3881,15 +2853,15 @@
         <v>180</v>
       </c>
       <c r="B60" s="1">
-        <v>67.231178283691406</v>
+        <v>68.363746643066406</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="1">
-        <v>190</v>
-      </c>
-      <c r="B61" s="2">
-        <v>71.097145080566406</v>
+        <v>180</v>
+      </c>
+      <c r="B61" s="1">
+        <v>67.231178283691406</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3897,7 +2869,7 @@
         <v>190</v>
       </c>
       <c r="B62" s="2">
-        <v>70.110191345214801</v>
+        <v>71.097145080566406</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3905,15 +2877,15 @@
         <v>190</v>
       </c>
       <c r="B63" s="2">
-        <v>69.957695007324205</v>
+        <v>70.110191345214801</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="1">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="B64" s="2">
-        <v>84.250335693359304</v>
+        <v>69.957695007324205</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3921,31 +2893,31 @@
         <v>225</v>
       </c>
       <c r="B65" s="2">
-        <v>82.887565612792898</v>
+        <v>84.250335693359304</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="1">
         <v>225</v>
       </c>
-      <c r="B66" s="1">
-        <v>83.120491027832003</v>
+      <c r="B66" s="2">
+        <v>82.887565612792898</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="1">
         <v>225</v>
       </c>
-      <c r="B67" s="2">
-        <v>82.969505310058594</v>
+      <c r="B67" s="1">
+        <v>83.120491027832003</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="1">
         <v>225</v>
       </c>
-      <c r="B68" s="1">
-        <v>84.640823364257798</v>
+      <c r="B68" s="2">
+        <v>82.969505310058594</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3953,23 +2925,23 @@
         <v>225</v>
       </c>
       <c r="B69" s="1">
-        <v>83.370384216308594</v>
+        <v>84.640823364257798</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="1">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="B70" s="1">
-        <v>92.075706481933594</v>
+        <v>83.370384216308594</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="1">
         <v>250</v>
       </c>
-      <c r="B71" s="2">
-        <v>90.467185974121094</v>
+      <c r="B71" s="1">
+        <v>92.075706481933594</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3977,15 +2949,15 @@
         <v>250</v>
       </c>
       <c r="B72" s="2">
-        <v>90.876480102539006</v>
+        <v>90.467185974121094</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="1">
         <v>250</v>
       </c>
-      <c r="B73" s="1">
-        <v>91.030120849609304</v>
+      <c r="B73" s="2">
+        <v>90.876480102539006</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -3993,7 +2965,7 @@
         <v>250</v>
       </c>
       <c r="B74" s="1">
-        <v>91.1021728515625</v>
+        <v>91.030120849609304</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4001,15 +2973,15 @@
         <v>250</v>
       </c>
       <c r="B75" s="1">
-        <v>90.482322692871094</v>
+        <v>91.1021728515625</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="1">
         <v>250</v>
       </c>
-      <c r="B76" s="2">
-        <v>91.2183837890625</v>
+      <c r="B76" s="1">
+        <v>90.482322692871094</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4017,31 +2989,31 @@
         <v>250</v>
       </c>
       <c r="B77" s="2">
-        <v>90.765350341796804</v>
+        <v>91.2183837890625</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="1">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="B78" s="2">
-        <v>98.324745178222599</v>
+        <v>90.765350341796804</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="1">
         <v>275</v>
       </c>
-      <c r="B79" s="1">
-        <v>97.644721984863196</v>
+      <c r="B79" s="2">
+        <v>98.324745178222599</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="1">
         <v>275</v>
       </c>
-      <c r="B80" s="2">
-        <v>98.625343322753906</v>
+      <c r="B80" s="1">
+        <v>97.644721984863196</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4049,7 +3021,7 @@
         <v>275</v>
       </c>
       <c r="B81" s="2">
-        <v>98.048446655273395</v>
+        <v>98.625343322753906</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4057,31 +3029,31 @@
         <v>275</v>
       </c>
       <c r="B82" s="2">
-        <v>97.541885375976506</v>
+        <v>98.048446655273395</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="1">
         <v>275</v>
       </c>
-      <c r="B83" s="1">
-        <v>98.221984863281193</v>
+      <c r="B83" s="2">
+        <v>97.541885375976506</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="1">
         <v>275</v>
       </c>
-      <c r="B84" s="2">
-        <v>98.3951416015625</v>
+      <c r="B84" s="1">
+        <v>98.221984863281193</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="1">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="B85" s="2">
-        <v>112.94920349121</v>
+        <v>98.3951416015625</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4089,7 +3061,7 @@
         <v>300</v>
       </c>
       <c r="B86" s="2">
-        <v>111.3111038208</v>
+        <v>112.94920349121</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4097,7 +3069,7 @@
         <v>300</v>
       </c>
       <c r="B87" s="2">
-        <v>111.458618164062</v>
+        <v>111.3111038208</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4105,7 +3077,7 @@
         <v>300</v>
       </c>
       <c r="B88" s="2">
-        <v>112.343132019042</v>
+        <v>111.458618164062</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4113,7 +3085,7 @@
         <v>300</v>
       </c>
       <c r="B89" s="2">
-        <v>113.33374786376901</v>
+        <v>112.343132019042</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4121,7 +3093,7 @@
         <v>300</v>
       </c>
       <c r="B90" s="2">
-        <v>111.86164855957</v>
+        <v>113.33374786376901</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4129,7 +3101,7 @@
         <v>300</v>
       </c>
       <c r="B91" s="2">
-        <v>112.181800842285</v>
+        <v>111.86164855957</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4137,15 +3109,15 @@
         <v>300</v>
       </c>
       <c r="B92" s="2">
-        <v>112.669151306152</v>
+        <v>112.181800842285</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="1">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="B93" s="2">
-        <v>119.597518920898</v>
+        <v>112.669151306152</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4153,7 +3125,7 @@
         <v>325</v>
       </c>
       <c r="B94" s="2">
-        <v>119.668937683105</v>
+        <v>119.597518920898</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4161,23 +3133,23 @@
         <v>325</v>
       </c>
       <c r="B95" s="2">
-        <v>118.55248260498</v>
+        <v>119.668937683105</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="1">
         <v>325</v>
       </c>
-      <c r="B96" s="1">
-        <v>120.087356567382</v>
+      <c r="B96" s="2">
+        <v>118.55248260498</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="1">
         <v>325</v>
       </c>
-      <c r="B97" s="2">
-        <v>120.041015625</v>
+      <c r="B97" s="1">
+        <v>120.087356567382</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4185,7 +3157,7 @@
         <v>325</v>
       </c>
       <c r="B98" s="2">
-        <v>117.07137298583901</v>
+        <v>120.041015625</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4193,7 +3165,7 @@
         <v>325</v>
       </c>
       <c r="B99" s="2">
-        <v>116.49659729003901</v>
+        <v>117.07137298583901</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4201,15 +3173,15 @@
         <v>325</v>
       </c>
       <c r="B100" s="2">
-        <v>119.387168884277</v>
+        <v>116.49659729003901</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="1">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="B101" s="2">
-        <v>134.02989196777301</v>
+        <v>119.387168884277</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4217,7 +3189,7 @@
         <v>350</v>
       </c>
       <c r="B102" s="2">
-        <v>129.77296447753901</v>
+        <v>134.02989196777301</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4225,7 +3197,7 @@
         <v>350</v>
       </c>
       <c r="B103" s="2">
-        <v>129.58163452148401</v>
+        <v>129.77296447753901</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4233,7 +3205,7 @@
         <v>350</v>
       </c>
       <c r="B104" s="2">
-        <v>129.39317321777301</v>
+        <v>129.58163452148401</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4241,7 +3213,7 @@
         <v>350</v>
       </c>
       <c r="B105" s="2">
-        <v>131.60490417480401</v>
+        <v>129.39317321777301</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4249,31 +3221,31 @@
         <v>350</v>
       </c>
       <c r="B106" s="2">
-        <v>128.85876464843699</v>
+        <v>131.60490417480401</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="1">
         <v>350</v>
       </c>
-      <c r="B107" s="1">
-        <v>130.38032531738199</v>
+      <c r="B107" s="2">
+        <v>128.85876464843699</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="1">
         <v>350</v>
       </c>
-      <c r="B108" s="2">
-        <v>129.2626953125</v>
+      <c r="B108" s="1">
+        <v>130.38032531738199</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="1">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="B109" s="2">
-        <v>141.05140686035099</v>
+        <v>129.2626953125</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4281,7 +3253,7 @@
         <v>375</v>
       </c>
       <c r="B110" s="2">
-        <v>139.86647033691401</v>
+        <v>141.05140686035099</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4289,7 +3261,7 @@
         <v>375</v>
       </c>
       <c r="B111" s="2">
-        <v>139.86706542968699</v>
+        <v>139.86647033691401</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4297,7 +3269,7 @@
         <v>375</v>
       </c>
       <c r="B112" s="2">
-        <v>139.56504821777301</v>
+        <v>139.86706542968699</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4305,7 +3277,7 @@
         <v>375</v>
       </c>
       <c r="B113" s="2">
-        <v>141.54527282714801</v>
+        <v>139.56504821777301</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4313,7 +3285,7 @@
         <v>375</v>
       </c>
       <c r="B114" s="2">
-        <v>139.04574584960901</v>
+        <v>141.54527282714801</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4321,7 +3293,7 @@
         <v>375</v>
       </c>
       <c r="B115" s="2">
-        <v>140.45903015136699</v>
+        <v>139.04574584960901</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4329,15 +3301,15 @@
         <v>375</v>
       </c>
       <c r="B116" s="2">
-        <v>139.50605773925699</v>
+        <v>140.45903015136699</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="1">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="B117" s="2">
-        <v>152.88243103027301</v>
+        <v>139.50605773925699</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4345,7 +3317,7 @@
         <v>400</v>
       </c>
       <c r="B118" s="2">
-        <v>146.42054748535099</v>
+        <v>152.88243103027301</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4353,7 +3325,7 @@
         <v>400</v>
       </c>
       <c r="B119" s="2">
-        <v>147.19046020507801</v>
+        <v>146.42054748535099</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4361,7 +3333,7 @@
         <v>400</v>
       </c>
       <c r="B120" s="2">
-        <v>146.21650695800699</v>
+        <v>147.19046020507801</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4369,7 +3341,7 @@
         <v>400</v>
       </c>
       <c r="B121" s="2">
-        <v>152.85513305664</v>
+        <v>146.21650695800699</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4377,7 +3349,7 @@
         <v>400</v>
       </c>
       <c r="B122" s="2">
-        <v>147.08241271972599</v>
+        <v>152.85513305664</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4385,7 +3357,7 @@
         <v>400</v>
       </c>
       <c r="B123" s="2">
-        <v>148.21440124511699</v>
+        <v>147.08241271972599</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4393,15 +3365,15 @@
         <v>400</v>
       </c>
       <c r="B124" s="2">
-        <v>146.92153930664</v>
+        <v>148.21440124511699</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="1">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="B125" s="2">
-        <v>157.809967041015</v>
+        <v>146.92153930664</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4409,7 +3381,7 @@
         <v>425</v>
       </c>
       <c r="B126" s="2">
-        <v>149.60018920898401</v>
+        <v>157.809967041015</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4417,7 +3389,7 @@
         <v>425</v>
       </c>
       <c r="B127" s="2">
-        <v>151.85455322265599</v>
+        <v>149.60018920898401</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4425,7 +3397,7 @@
         <v>425</v>
       </c>
       <c r="B128" s="2">
-        <v>149.95365905761699</v>
+        <v>151.85455322265599</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4433,7 +3405,7 @@
         <v>425</v>
       </c>
       <c r="B129" s="2">
-        <v>157.86619567871</v>
+        <v>149.95365905761699</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4441,7 +3413,7 @@
         <v>425</v>
       </c>
       <c r="B130" s="2">
-        <v>151.080307006835</v>
+        <v>157.86619567871</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4449,7 +3421,7 @@
         <v>425</v>
       </c>
       <c r="B131" s="2">
-        <v>151.45597839355401</v>
+        <v>151.080307006835</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4457,15 +3429,15 @@
         <v>425</v>
       </c>
       <c r="B132" s="2">
-        <v>151.01095581054599</v>
+        <v>151.45597839355401</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="1">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="B133" s="2">
-        <v>166.29953002929599</v>
+        <v>151.01095581054599</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4473,7 +3445,7 @@
         <v>450</v>
       </c>
       <c r="B134" s="2">
-        <v>157.990142822265</v>
+        <v>166.29953002929599</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4481,7 +3453,7 @@
         <v>450</v>
       </c>
       <c r="B135" s="2">
-        <v>160.46636962890599</v>
+        <v>157.990142822265</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4489,7 +3461,7 @@
         <v>450</v>
       </c>
       <c r="B136" s="2">
-        <v>158.114486694335</v>
+        <v>160.46636962890599</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4497,7 +3469,7 @@
         <v>450</v>
       </c>
       <c r="B137" s="2">
-        <v>164.97518920898401</v>
+        <v>158.114486694335</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4505,7 +3477,7 @@
         <v>450</v>
       </c>
       <c r="B138" s="2">
-        <v>157.52406311035099</v>
+        <v>164.97518920898401</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4513,7 +3485,7 @@
         <v>450</v>
       </c>
       <c r="B139" s="2">
-        <v>159.21244812011699</v>
+        <v>157.52406311035099</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4521,15 +3493,15 @@
         <v>450</v>
       </c>
       <c r="B140" s="2">
-        <v>156.62593078613199</v>
+        <v>159.21244812011699</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="1">
-        <v>75</v>
+        <v>450</v>
       </c>
       <c r="B141" s="2">
-        <v>30.01362991333</v>
+        <v>156.62593078613199</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4537,7 +3509,7 @@
         <v>75</v>
       </c>
       <c r="B142" s="2">
-        <v>26.8815097808837</v>
+        <v>30.01362991333</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4545,7 +3517,7 @@
         <v>75</v>
       </c>
       <c r="B143" s="2">
-        <v>29.338521957397401</v>
+        <v>26.8815097808837</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4553,7 +3525,7 @@
         <v>75</v>
       </c>
       <c r="B144" s="2">
-        <v>26.9236145019531</v>
+        <v>29.338521957397401</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4561,7 +3533,7 @@
         <v>75</v>
       </c>
       <c r="B145" s="2">
-        <v>29.346654891967699</v>
+        <v>26.9236145019531</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4569,7 +3541,7 @@
         <v>75</v>
       </c>
       <c r="B146" s="2">
-        <v>26.952102661132798</v>
+        <v>29.346654891967699</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -4577,14 +3549,22 @@
         <v>75</v>
       </c>
       <c r="B147" s="2">
-        <v>29.3502292633056</v>
+        <v>26.952102661132798</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="1">
         <v>75</v>
       </c>
-      <c r="B148" s="1">
+      <c r="B148" s="2">
+        <v>29.3502292633056</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A149" s="1">
+        <v>75</v>
+      </c>
+      <c r="B149" s="1">
         <v>26.5060520172119</v>
       </c>
     </row>
